--- a/outputs/Заявки в Корею.xlsx
+++ b/outputs/Заявки в Корею.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ИТОГО" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАЯВКА 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАЯВКА 2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАЯВКА 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ЗАЯВКА 2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,81 +443,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Заявка</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Позиций</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Штук</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Заявка 1 — наш ассортимент и потребность покупателя</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>149</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>35300</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Заявка 2 — из черновика инвойса Аннеси</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>382</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>88361</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>ВСЕГО</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>531</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>123661</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -597,8 +521,6 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -623,8 +545,6 @@
         <v>200</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -649,8 +569,6 @@
         <v>100</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -675,8 +593,6 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -701,8 +617,6 @@
         <v>200</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -727,8 +641,6 @@
         <v>100</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -753,8 +665,6 @@
         <v>100</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -779,8 +689,6 @@
         <v>100</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -805,8 +713,6 @@
         <v>1000</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -831,8 +737,6 @@
         <v>300</v>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -843,7 +747,6 @@
           <t>CELIMAX</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Celimax Dual Barrier Creamy Toner, 150</t>
@@ -853,8 +756,6 @@
         <v>500</v>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -865,7 +766,6 @@
           <t>DEOPROCE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>DEOPROCE RINSE - BLACK GARLIC INTENSME ENERGY [1000ml]</t>
@@ -875,8 +775,6 @@
         <v>100</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -887,7 +785,6 @@
           <t>DEOPROCE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]</t>
@@ -897,8 +794,6 @@
         <v>100</v>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -909,7 +804,6 @@
           <t>DEOPROCE</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]</t>
@@ -919,8 +813,6 @@
         <v>100</v>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -931,7 +823,6 @@
           <t>ELIZAVECCA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treatment [100ml]</t>
@@ -941,8 +832,6 @@
         <v>100</v>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -953,7 +842,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen 3in1 Sun Cream</t>
@@ -963,8 +851,6 @@
         <v>100</v>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -975,7 +861,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Moisture Essential Cream [50ml]</t>
@@ -985,8 +870,6 @@
         <v>800</v>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -997,7 +880,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g]</t>
@@ -1007,8 +889,6 @@
         <v>100</v>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1033,8 +913,6 @@
         <v>200</v>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1059,8 +937,6 @@
         <v>200</v>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1085,8 +961,6 @@
         <v>100</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1111,8 +985,6 @@
         <v>100</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1137,8 +1009,6 @@
         <v>100</v>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1163,8 +1033,6 @@
         <v>100</v>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1189,8 +1057,6 @@
         <v>100</v>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1215,8 +1081,6 @@
         <v>100</v>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1241,8 +1105,6 @@
         <v>100</v>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1267,8 +1129,6 @@
         <v>100</v>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1293,8 +1153,6 @@
         <v>100</v>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1319,8 +1177,6 @@
         <v>100</v>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1345,8 +1201,6 @@
         <v>100</v>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1371,8 +1225,6 @@
         <v>100</v>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1397,8 +1249,6 @@
         <v>100</v>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1423,8 +1273,6 @@
         <v>100</v>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1449,8 +1297,6 @@
         <v>100</v>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1475,8 +1321,6 @@
         <v>100</v>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1501,8 +1345,6 @@
         <v>100</v>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1527,8 +1369,6 @@
         <v>3000</v>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1553,8 +1393,6 @@
         <v>3000</v>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1579,8 +1417,6 @@
         <v>800</v>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1605,8 +1441,6 @@
         <v>100</v>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1631,8 +1465,6 @@
         <v>100</v>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1657,8 +1489,6 @@
         <v>300</v>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1683,8 +1513,6 @@
         <v>400</v>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1709,8 +1537,6 @@
         <v>100</v>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1735,8 +1561,6 @@
         <v>100</v>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1761,8 +1585,6 @@
         <v>100</v>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1773,7 +1595,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #01 [9g]</t>
@@ -1783,8 +1604,6 @@
         <v>100</v>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1795,7 +1614,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]</t>
@@ -1805,8 +1623,6 @@
         <v>100</v>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1817,7 +1633,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]</t>
@@ -1827,8 +1642,6 @@
         <v>100</v>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1853,8 +1666,6 @@
         <v>300</v>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1879,8 +1690,6 @@
         <v>300</v>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1905,8 +1714,6 @@
         <v>100</v>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1931,8 +1738,6 @@
         <v>200</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1957,8 +1762,6 @@
         <v>200</v>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1983,8 +1786,6 @@
         <v>100</v>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2009,8 +1810,6 @@
         <v>100</v>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2035,8 +1834,6 @@
         <v>400</v>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2061,8 +1858,6 @@
         <v>300</v>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2073,7 +1868,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Enough 8 Peptide Sensation Pro Balancing Cream</t>
@@ -2083,8 +1877,6 @@
         <v>100</v>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2095,7 +1887,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Enough 8 Peptide Sensation Pro Sun Cream</t>
@@ -2105,8 +1896,6 @@
         <v>100</v>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2117,7 +1906,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Enough Collagen Moisture Essential Cream</t>
@@ -2127,8 +1915,6 @@
         <v>100</v>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2139,7 +1925,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Enough Rich Gold Intensive Pro Nourishing Cream</t>
@@ -2149,8 +1934,6 @@
         <v>100</v>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2161,7 +1944,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>Enough Ultra X10 Collagen Pro Marine Cream</t>
@@ -2171,8 +1953,6 @@
         <v>100</v>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2183,7 +1963,6 @@
           <t>ENOUGH</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Enough gold snail moisture foundation 23</t>
@@ -2193,8 +1972,6 @@
         <v>100</v>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2205,7 +1982,6 @@
           <t>ETUDE</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
@@ -2215,8 +1991,6 @@
         <v>800</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2241,8 +2015,6 @@
         <v>300</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2267,8 +2039,6 @@
         <v>300</v>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2293,8 +2063,6 @@
         <v>600</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2319,8 +2087,6 @@
         <v>100</v>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2345,8 +2111,6 @@
         <v>100</v>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2371,8 +2135,6 @@
         <v>100</v>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2397,8 +2159,6 @@
         <v>400</v>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2423,8 +2183,6 @@
         <v>100</v>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2449,8 +2207,6 @@
         <v>100</v>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2475,8 +2231,6 @@
         <v>100</v>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2501,8 +2255,6 @@
         <v>100</v>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2527,8 +2279,6 @@
         <v>100</v>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2553,8 +2303,6 @@
         <v>200</v>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2579,8 +2327,6 @@
         <v>100</v>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2605,8 +2351,6 @@
         <v>100</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2631,8 +2375,6 @@
         <v>100</v>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2657,8 +2399,6 @@
         <v>100</v>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2683,8 +2423,6 @@
         <v>100</v>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2709,8 +2447,6 @@
         <v>100</v>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2735,8 +2471,6 @@
         <v>100</v>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2761,8 +2495,6 @@
         <v>100</v>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2787,8 +2519,6 @@
         <v>100</v>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2813,8 +2543,6 @@
         <v>100</v>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2839,8 +2567,6 @@
         <v>100</v>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2865,8 +2591,6 @@
         <v>100</v>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2891,8 +2615,6 @@
         <v>100</v>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2917,8 +2639,6 @@
         <v>100</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2943,8 +2663,6 @@
         <v>100</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2969,8 +2687,6 @@
         <v>100</v>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2995,8 +2711,6 @@
         <v>800</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3021,8 +2735,6 @@
         <v>100</v>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3047,8 +2759,6 @@
         <v>100</v>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3073,8 +2783,6 @@
         <v>100</v>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3085,7 +2793,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>JMSOLUTION - Active Birds Nest Moisture Mask [30ml*10ea]</t>
@@ -3095,8 +2802,6 @@
         <v>100</v>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3107,7 +2812,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>JMSOLUTION - Active Golden Caviar Nourishing Mask [30ml*10ea]</t>
@@ -3117,8 +2821,6 @@
         <v>100</v>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3129,7 +2831,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>JMSOLUTION - Active Jellyfish Vital Mask [30ml*10ea]</t>
@@ -3139,8 +2840,6 @@
         <v>100</v>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3165,8 +2864,6 @@
         <v>100</v>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3177,7 +2874,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>JMSOLUTION - MASK PACK DISNEY [30ml*10ea] 10</t>
@@ -3187,8 +2883,6 @@
         <v>100</v>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3199,7 +2893,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>JMSOLUTION - The Natural Cordyceps Melitaris Mask Moisture [30ml*10ea]</t>
@@ -3209,8 +2902,6 @@
         <v>100</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3221,7 +2912,6 @@
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>JMSOLUTION - Water Luminous S.O.S. Ringer Mask Black [35ml*10ea]</t>
@@ -3231,8 +2921,6 @@
         <v>100</v>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3257,8 +2945,6 @@
         <v>100</v>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3283,8 +2969,6 @@
         <v>100</v>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3309,8 +2993,6 @@
         <v>100</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3335,8 +3017,6 @@
         <v>100</v>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3361,8 +3041,6 @@
         <v>100</v>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3387,8 +3065,6 @@
         <v>100</v>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3413,8 +3089,6 @@
         <v>600</v>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3439,8 +3113,6 @@
         <v>1400</v>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3465,8 +3137,6 @@
         <v>800</v>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3477,7 +3147,6 @@
           <t>MANYO</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>MANYO - Pure Cleansing Oil [200ml]</t>
@@ -3487,8 +3156,6 @@
         <v>100</v>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3513,8 +3180,6 @@
         <v>700</v>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3539,8 +3204,6 @@
         <v>600</v>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3551,7 +3214,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
@@ -3561,8 +3223,6 @@
         <v>400</v>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3587,8 +3247,6 @@
         <v>600</v>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3599,7 +3257,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
@@ -3609,8 +3266,6 @@
         <v>200</v>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3635,8 +3290,6 @@
         <v>100</v>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3647,7 +3300,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
@@ -3657,8 +3309,6 @@
         <v>100</v>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3669,7 +3319,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
@@ -3679,8 +3328,6 @@
         <v>200</v>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3691,7 +3338,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
@@ -3701,8 +3347,6 @@
         <v>300</v>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3727,8 +3371,6 @@
         <v>200</v>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3753,8 +3395,6 @@
         <v>100</v>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3765,7 +3405,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
@@ -3775,8 +3414,6 @@
         <v>100</v>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3787,7 +3424,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
@@ -3797,8 +3433,6 @@
         <v>100</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3809,7 +3443,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
@@ -3819,8 +3452,6 @@
         <v>100</v>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3845,8 +3476,6 @@
         <v>400</v>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3871,8 +3500,6 @@
         <v>100</v>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3897,8 +3524,6 @@
         <v>100</v>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3923,8 +3548,6 @@
         <v>200</v>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3935,7 +3558,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
@@ -3945,8 +3567,6 @@
         <v>400</v>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3971,8 +3591,6 @@
         <v>400</v>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3997,8 +3615,6 @@
         <v>400</v>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4009,7 +3625,6 @@
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
@@ -4019,8 +3634,6 @@
         <v>100</v>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4031,7 +3644,6 @@
           <t>PRRETI</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>PRRETI Honey&amp;Berry Lip Sleeping Mask 15</t>
@@ -4041,8 +3653,6 @@
         <v>200</v>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4067,8 +3677,6 @@
         <v>700</v>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4093,8 +3701,6 @@
         <v>100</v>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4119,8 +3725,6 @@
         <v>100</v>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4145,8 +3749,6 @@
         <v>200</v>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4171,8 +3773,6 @@
         <v>100</v>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4197,8 +3797,6 @@
         <v>100</v>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4223,8 +3821,6 @@
         <v>100</v>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4235,7 +3831,6 @@
           <t>THE</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml]</t>
@@ -4245,8 +3840,6 @@
         <v>100</v>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4257,7 +3850,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>VT PDRN ESSENCE 100</t>
@@ -4267,8 +3859,6 @@
         <v>100</v>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4293,8 +3883,6 @@
         <v>100</v>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr"/>
@@ -4317,7 +3905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4407,9 +3995,6 @@
         <v>162</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4434,9 +4019,6 @@
         <v>162</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4461,8 +4043,6 @@
         <v>162</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>8809562191070 / 8809562192909</t>
@@ -4492,9 +4072,6 @@
         <v>162</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4519,9 +4096,6 @@
         <v>162</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4546,9 +4120,6 @@
         <v>168</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4573,9 +4144,6 @@
         <v>252</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4600,9 +4168,6 @@
         <v>160</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4627,9 +4192,6 @@
         <v>168</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4654,9 +4216,6 @@
         <v>252</v>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4681,9 +4240,6 @@
         <v>108</v>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4708,9 +4264,6 @@
         <v>108</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4735,9 +4288,6 @@
         <v>108</v>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4762,9 +4312,6 @@
         <v>108</v>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4789,9 +4336,6 @@
         <v>168</v>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4816,9 +4360,6 @@
         <v>252</v>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4843,9 +4384,6 @@
         <v>162</v>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4870,9 +4408,6 @@
         <v>210</v>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4897,9 +4432,6 @@
         <v>150</v>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4924,9 +4456,6 @@
         <v>500</v>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4951,9 +4480,6 @@
         <v>540</v>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4978,9 +4504,6 @@
         <v>540</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5005,9 +4528,6 @@
         <v>540</v>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -5032,9 +4552,6 @@
         <v>300</v>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -5059,9 +4576,6 @@
         <v>150</v>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -5086,9 +4600,6 @@
         <v>180</v>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5113,9 +4624,6 @@
         <v>800</v>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5140,9 +4648,6 @@
         <v>216</v>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -5167,9 +4672,6 @@
         <v>360</v>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5194,9 +4696,6 @@
         <v>360</v>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5221,9 +4720,6 @@
         <v>360</v>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5248,9 +4744,6 @@
         <v>160</v>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5275,9 +4768,6 @@
         <v>96</v>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5302,9 +4792,6 @@
         <v>135</v>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5329,9 +4816,6 @@
         <v>216</v>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5356,9 +4840,6 @@
         <v>165</v>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5383,9 +4864,6 @@
         <v>270</v>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5410,9 +4888,6 @@
         <v>195</v>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5437,9 +4912,6 @@
         <v>990</v>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5464,9 +4936,6 @@
         <v>990</v>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5491,9 +4960,6 @@
         <v>990</v>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5518,9 +4984,6 @@
         <v>990</v>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5545,9 +5008,6 @@
         <v>990</v>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5572,9 +5032,6 @@
         <v>48</v>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5599,9 +5056,6 @@
         <v>48</v>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5626,9 +5080,6 @@
         <v>60</v>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5653,9 +5104,6 @@
         <v>300</v>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5680,9 +5128,6 @@
         <v>200</v>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5707,9 +5152,6 @@
         <v>200</v>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5734,9 +5176,6 @@
         <v>200</v>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5761,9 +5200,6 @@
         <v>400</v>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5788,9 +5224,6 @@
         <v>84</v>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5815,9 +5248,6 @@
         <v>84</v>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5842,8 +5272,6 @@
         <v>180</v>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>8803463007416 / 8803463010027</t>
@@ -5873,9 +5301,6 @@
         <v>180</v>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5900,9 +5325,6 @@
         <v>180</v>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5927,9 +5349,6 @@
         <v>400</v>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5954,9 +5373,6 @@
         <v>400</v>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5981,9 +5397,6 @@
         <v>400</v>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6008,9 +5421,6 @@
         <v>42</v>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6035,9 +5445,6 @@
         <v>200</v>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6062,8 +5469,6 @@
         <v>200</v>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>8803463007416 / 8803463010027</t>
@@ -6093,9 +5498,6 @@
         <v>200</v>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6120,9 +5522,6 @@
         <v>200</v>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6147,9 +5546,6 @@
         <v>200</v>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -6174,9 +5570,6 @@
         <v>78</v>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -6201,8 +5594,6 @@
         <v>78</v>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>8803463007416 / 8803463010027</t>
@@ -6232,9 +5623,6 @@
         <v>78</v>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6259,9 +5647,6 @@
         <v>78</v>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6286,9 +5671,6 @@
         <v>78</v>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6313,9 +5695,6 @@
         <v>168</v>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6340,9 +5719,6 @@
         <v>168</v>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6367,8 +5743,6 @@
         <v>84</v>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>8803463006396 / 8803463007249</t>
@@ -6398,8 +5772,6 @@
         <v>84</v>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>8803463006402 / 8803463007256</t>
@@ -6429,8 +5801,6 @@
         <v>84</v>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>8803463003692 / 8803463007317</t>
@@ -6460,9 +5830,6 @@
         <v>540</v>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6487,9 +5854,6 @@
         <v>540</v>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6514,9 +5878,6 @@
         <v>540</v>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6541,9 +5902,6 @@
         <v>540</v>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6568,9 +5926,6 @@
         <v>48</v>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6595,9 +5950,6 @@
         <v>48</v>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6622,8 +5974,6 @@
         <v>48</v>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>8803463006396 / 8803463007249</t>
@@ -6653,9 +6003,6 @@
         <v>48</v>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6680,9 +6027,6 @@
         <v>48</v>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6707,8 +6051,6 @@
         <v>48</v>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>8803463006402 / 8803463007256</t>
@@ -6738,9 +6080,6 @@
         <v>48</v>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6765,9 +6104,6 @@
         <v>48</v>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6792,8 +6128,6 @@
         <v>48</v>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>8803463003692 / 8803463007317</t>
@@ -6823,9 +6157,6 @@
         <v>48</v>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6850,9 +6181,6 @@
         <v>48</v>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6877,8 +6205,6 @@
         <v>48</v>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>8803463003685 / 8803463007324</t>
@@ -6908,9 +6234,6 @@
         <v>48</v>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6935,9 +6258,6 @@
         <v>48</v>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6962,9 +6282,6 @@
         <v>48</v>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6989,9 +6306,6 @@
         <v>48</v>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7016,9 +6330,6 @@
         <v>48</v>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7043,9 +6354,6 @@
         <v>48</v>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7070,9 +6378,6 @@
         <v>48</v>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7097,9 +6402,6 @@
         <v>144</v>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7124,9 +6426,6 @@
         <v>144</v>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7151,9 +6450,6 @@
         <v>72</v>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7178,9 +6474,6 @@
         <v>96</v>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7205,9 +6498,6 @@
         <v>360</v>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7232,9 +6522,6 @@
         <v>560</v>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7259,9 +6546,6 @@
         <v>78</v>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7286,9 +6570,6 @@
         <v>120</v>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7313,8 +6594,6 @@
         <v>144</v>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>8803463006655 / 8803463020040</t>
@@ -7344,9 +6623,6 @@
         <v>96</v>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7371,9 +6647,6 @@
         <v>96</v>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7384,7 +6657,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>KR_PD_PDRN TONER_250ml_1ea</t>
@@ -7394,9 +6666,6 @@
         <v>96</v>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7421,9 +6690,6 @@
         <v>96</v>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7448,9 +6714,6 @@
         <v>108</v>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7475,9 +6738,6 @@
         <v>96</v>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7502,9 +6762,6 @@
         <v>96</v>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7529,9 +6786,6 @@
         <v>144</v>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7556,9 +6810,6 @@
         <v>288</v>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7583,9 +6834,6 @@
         <v>48</v>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7610,9 +6858,6 @@
         <v>60</v>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7637,9 +6882,6 @@
         <v>60</v>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7664,9 +6906,6 @@
         <v>60</v>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7677,7 +6916,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>KR_OL_CRYO ICE MASK_320g_30ea</t>
@@ -7687,9 +6925,6 @@
         <v>36</v>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7714,9 +6949,6 @@
         <v>900</v>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7741,9 +6973,6 @@
         <v>120</v>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7768,9 +6997,6 @@
         <v>216</v>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7795,9 +7021,6 @@
         <v>192</v>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7822,9 +7045,6 @@
         <v>840</v>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7835,7 +7055,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>VT CICA RETI-A ALL IN ONE 3STEP MASK</t>
@@ -7845,9 +7064,6 @@
         <v>560</v>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7872,9 +7088,6 @@
         <v>120</v>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7899,9 +7112,6 @@
         <v>168</v>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7926,9 +7136,6 @@
         <v>48</v>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7953,9 +7160,6 @@
         <v>48</v>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7980,9 +7184,6 @@
         <v>48</v>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7993,7 +7194,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>VT PRO CICA CENTELLA ASIATICA TIGER CLEAR SPOT PATCH 4pcs/15ea*2+18ea*2(66EA)</t>
@@ -8003,9 +7203,6 @@
         <v>50</v>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8016,7 +7213,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>VT SPOT PATCH(3sets, 48ea)</t>
@@ -8026,9 +7222,6 @@
         <v>1000</v>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8053,9 +7246,6 @@
         <v>60</v>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8080,9 +7270,6 @@
         <v>112</v>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8107,9 +7294,6 @@
         <v>96</v>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8134,9 +7318,6 @@
         <v>48</v>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8161,9 +7342,6 @@
         <v>48</v>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8188,9 +7366,6 @@
         <v>144</v>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8201,7 +7376,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>VT CICA COLLAGEN ALL IN ONE 3STEP MASK</t>
@@ -8211,9 +7385,6 @@
         <v>560</v>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8238,9 +7409,6 @@
         <v>48</v>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8265,9 +7433,6 @@
         <v>240</v>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8292,9 +7457,6 @@
         <v>192</v>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8305,7 +7467,6 @@
           <t>VT</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>VT VITA-LIGHT ALL IN ONE 3STEP MASK</t>
@@ -8315,9 +7476,6 @@
         <v>560</v>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8342,9 +7500,6 @@
         <v>48</v>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8369,9 +7524,6 @@
         <v>192</v>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8396,9 +7548,6 @@
         <v>192</v>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8423,9 +7572,6 @@
         <v>192</v>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8450,9 +7596,6 @@
         <v>192</v>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8477,9 +7620,6 @@
         <v>96</v>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8504,9 +7644,6 @@
         <v>96</v>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8531,9 +7668,6 @@
         <v>48</v>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8558,9 +7692,6 @@
         <v>96</v>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8585,9 +7716,6 @@
         <v>144</v>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8612,9 +7740,6 @@
         <v>108</v>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8639,9 +7764,6 @@
         <v>96</v>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8666,9 +7788,6 @@
         <v>96</v>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8693,9 +7812,6 @@
         <v>96</v>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8720,9 +7836,6 @@
         <v>80</v>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8747,9 +7860,6 @@
         <v>48</v>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8774,9 +7884,6 @@
         <v>96</v>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8801,9 +7908,6 @@
         <v>48</v>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8828,9 +7932,6 @@
         <v>48</v>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8855,9 +7956,6 @@
         <v>48</v>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8882,9 +7980,6 @@
         <v>120</v>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8909,9 +8004,6 @@
         <v>72</v>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8936,9 +8028,6 @@
         <v>48</v>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8963,9 +8052,6 @@
         <v>180</v>
       </c>
       <c r="F170" s="2" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8990,9 +8076,6 @@
         <v>96</v>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9017,9 +8100,6 @@
         <v>72</v>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9044,9 +8124,6 @@
         <v>144</v>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -9071,9 +8148,6 @@
         <v>144</v>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -9098,9 +8172,6 @@
         <v>144</v>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9125,9 +8196,6 @@
         <v>144</v>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9152,9 +8220,6 @@
         <v>48</v>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9179,9 +8244,6 @@
         <v>432</v>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9206,9 +8268,6 @@
         <v>576</v>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9233,9 +8292,6 @@
         <v>432</v>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9260,9 +8316,6 @@
         <v>576</v>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9287,9 +8340,6 @@
         <v>432</v>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9314,9 +8364,6 @@
         <v>720</v>
       </c>
       <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9341,9 +8388,6 @@
         <v>288</v>
       </c>
       <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9368,9 +8412,6 @@
         <v>576</v>
       </c>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9395,9 +8436,6 @@
         <v>576</v>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9422,9 +8460,6 @@
         <v>90</v>
       </c>
       <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9449,9 +8484,6 @@
         <v>60</v>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9476,9 +8508,6 @@
         <v>60</v>
       </c>
       <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9503,9 +8532,6 @@
         <v>60</v>
       </c>
       <c r="F190" s="2" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9530,9 +8556,6 @@
         <v>216</v>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9557,9 +8580,6 @@
         <v>300</v>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9584,9 +8604,6 @@
         <v>360</v>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9611,9 +8628,6 @@
         <v>320</v>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9638,9 +8652,6 @@
         <v>90</v>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9665,9 +8676,6 @@
         <v>640</v>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9692,9 +8700,6 @@
         <v>640</v>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9719,9 +8724,6 @@
         <v>144</v>
       </c>
       <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9746,9 +8748,6 @@
         <v>800</v>
       </c>
       <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9773,9 +8772,6 @@
         <v>320</v>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9800,9 +8796,6 @@
         <v>240</v>
       </c>
       <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9827,9 +8820,6 @@
         <v>300</v>
       </c>
       <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9854,9 +8844,6 @@
         <v>300</v>
       </c>
       <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9881,9 +8868,6 @@
         <v>80</v>
       </c>
       <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9908,9 +8892,6 @@
         <v>360</v>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9935,9 +8916,6 @@
         <v>360</v>
       </c>
       <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -9962,9 +8940,6 @@
         <v>360</v>
       </c>
       <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -9989,9 +8964,6 @@
         <v>880</v>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10016,9 +8988,6 @@
         <v>880</v>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10029,7 +8998,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>Koelf Lemon &amp; Basil Ice Pop Hydrogel Eye Mask</t>
@@ -10039,9 +9007,6 @@
         <v>216</v>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10052,7 +9017,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>Koelf Blueberry &amp; Cream Ice Pop Hydrogel Eye Mask</t>
@@ -10062,9 +9026,6 @@
         <v>216</v>
       </c>
       <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10075,7 +9036,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>Koelf Ruby &amp; Bulgarian Rose Hydrogel Eye Patch</t>
@@ -10085,9 +9045,6 @@
         <v>216</v>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10098,7 +9055,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>Koelf Gold &amp; Royal Jelly Hydrogel Eye Patch</t>
@@ -10108,9 +9064,6 @@
         <v>216</v>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10121,7 +9074,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>Koelf Pearl &amp; Shea Butter Hydrogel Eye Patch</t>
@@ -10131,9 +9083,6 @@
         <v>216</v>
       </c>
       <c r="F214" s="2" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10144,7 +9093,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>Koelf Melting Essence Hand Pack (10 uses)</t>
@@ -10154,9 +9102,6 @@
         <v>72</v>
       </c>
       <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -10167,7 +9112,6 @@
           <t>Koelf</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>Koelf Melting Essence Foot Pack (10 uses)</t>
@@ -10177,9 +9121,6 @@
         <v>72</v>
       </c>
       <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -10204,9 +9145,6 @@
         <v>300</v>
       </c>
       <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10231,9 +9169,6 @@
         <v>300</v>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10258,9 +9193,6 @@
         <v>300</v>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -10285,9 +9217,6 @@
         <v>200</v>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10312,9 +9241,6 @@
         <v>200</v>
       </c>
       <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10339,9 +9265,6 @@
         <v>200</v>
       </c>
       <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10366,9 +9289,6 @@
         <v>400</v>
       </c>
       <c r="F223" s="2" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10393,8 +9313,6 @@
         <v>400</v>
       </c>
       <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>8809733213655 / 8809733213679</t>
@@ -10424,9 +9342,6 @@
         <v>400</v>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10451,8 +9366,6 @@
         <v>400</v>
       </c>
       <c r="F226" s="2" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>8809733213655 / 8809733213679</t>
@@ -10482,9 +9395,6 @@
         <v>400</v>
       </c>
       <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10509,9 +9419,6 @@
         <v>80</v>
       </c>
       <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10536,9 +9443,6 @@
         <v>80</v>
       </c>
       <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10563,9 +9467,6 @@
         <v>80</v>
       </c>
       <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10590,9 +9491,6 @@
         <v>80</v>
       </c>
       <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10617,9 +9515,6 @@
         <v>80</v>
       </c>
       <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10644,9 +9539,6 @@
         <v>80</v>
       </c>
       <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10671,9 +9563,6 @@
         <v>80</v>
       </c>
       <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10698,9 +9587,6 @@
         <v>60</v>
       </c>
       <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10725,9 +9611,6 @@
         <v>60</v>
       </c>
       <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10752,9 +9635,6 @@
         <v>60</v>
       </c>
       <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10779,9 +9659,6 @@
         <v>60</v>
       </c>
       <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10806,9 +9683,6 @@
         <v>200</v>
       </c>
       <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10833,9 +9707,6 @@
         <v>200</v>
       </c>
       <c r="F240" s="2" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10860,9 +9731,6 @@
         <v>200</v>
       </c>
       <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -10887,9 +9755,6 @@
         <v>400</v>
       </c>
       <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -10914,9 +9779,6 @@
         <v>800</v>
       </c>
       <c r="F243" s="2" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -10941,9 +9803,6 @@
         <v>640</v>
       </c>
       <c r="F244" s="2" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -10968,9 +9827,6 @@
         <v>1200</v>
       </c>
       <c r="F245" s="2" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -10995,8 +9851,6 @@
         <v>120</v>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>8809941826302 / 8809941826555</t>
@@ -11026,8 +9880,6 @@
         <v>252</v>
       </c>
       <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>8809941826579 / 8809941826586</t>
@@ -11057,8 +9909,6 @@
         <v>126</v>
       </c>
       <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>8809941826319 / 8809941826562</t>
@@ -11088,9 +9938,6 @@
         <v>50</v>
       </c>
       <c r="F249" s="2" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11115,8 +9962,6 @@
         <v>60</v>
       </c>
       <c r="F250" s="2" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>8809941825794 / 8809941827316</t>
@@ -11146,9 +9991,6 @@
         <v>80</v>
       </c>
       <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11173,9 +10015,6 @@
         <v>50</v>
       </c>
       <c r="F252" s="2" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11200,9 +10039,6 @@
         <v>200</v>
       </c>
       <c r="F253" s="2" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11227,9 +10063,6 @@
         <v>80</v>
       </c>
       <c r="F254" s="2" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11254,9 +10087,6 @@
         <v>90</v>
       </c>
       <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11281,9 +10111,6 @@
         <v>60</v>
       </c>
       <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11308,9 +10135,6 @@
         <v>60</v>
       </c>
       <c r="F257" s="2" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11335,9 +10159,6 @@
         <v>160</v>
       </c>
       <c r="F258" s="2" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11362,9 +10183,6 @@
         <v>50</v>
       </c>
       <c r="F259" s="2" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11389,9 +10207,6 @@
         <v>56</v>
       </c>
       <c r="F260" s="2" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11416,9 +10231,6 @@
         <v>80</v>
       </c>
       <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11443,9 +10255,6 @@
         <v>40</v>
       </c>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -11470,9 +10279,6 @@
         <v>40</v>
       </c>
       <c r="F263" s="2" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -11497,8 +10303,6 @@
         <v>60</v>
       </c>
       <c r="F264" s="2" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>8809941820430 / 8809941826722</t>
@@ -11528,9 +10332,6 @@
         <v>200</v>
       </c>
       <c r="F265" s="2" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -11555,8 +10356,6 @@
         <v>36</v>
       </c>
       <c r="F266" s="2" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>8809409345758 / 8809941827323</t>
@@ -11586,8 +10385,6 @@
         <v>60</v>
       </c>
       <c r="F267" s="2" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>8809409347004 / 8809941827309</t>
@@ -11617,8 +10414,6 @@
         <v>40</v>
       </c>
       <c r="F268" s="2" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>8809409340944 / 8809941820270</t>
@@ -11648,9 +10443,6 @@
         <v>96</v>
       </c>
       <c r="F269" s="2" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -11675,9 +10467,6 @@
         <v>12</v>
       </c>
       <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -11702,9 +10491,6 @@
         <v>48</v>
       </c>
       <c r="F271" s="2" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -11729,9 +10515,6 @@
         <v>63</v>
       </c>
       <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -11756,8 +10539,6 @@
         <v>30</v>
       </c>
       <c r="F273" s="2" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>8809941825008 / 8809941825060</t>
@@ -11787,9 +10568,6 @@
         <v>24</v>
       </c>
       <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -11814,9 +10592,6 @@
         <v>56</v>
       </c>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -11841,8 +10616,6 @@
         <v>24</v>
       </c>
       <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>8809941822342 / 8809941827347</t>
@@ -11872,9 +10645,6 @@
         <v>240</v>
       </c>
       <c r="F277" s="2" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -11899,9 +10669,6 @@
         <v>72</v>
       </c>
       <c r="F278" s="2" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -11926,9 +10693,6 @@
         <v>56</v>
       </c>
       <c r="F279" s="2" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -11953,8 +10717,6 @@
         <v>40</v>
       </c>
       <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>8809941821734 / 8809941826609</t>
@@ -11984,8 +10746,6 @@
         <v>24</v>
       </c>
       <c r="F281" s="2" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>8809409340098 / 8809409340975</t>
@@ -12015,8 +10775,6 @@
         <v>40</v>
       </c>
       <c r="F282" s="2" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>8809409340098 / 8809409340975</t>
@@ -12046,9 +10804,6 @@
         <v>28</v>
       </c>
       <c r="F283" s="2" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -12073,9 +10828,6 @@
         <v>240</v>
       </c>
       <c r="F284" s="2" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -12100,9 +10852,6 @@
         <v>30</v>
       </c>
       <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -12127,9 +10876,6 @@
         <v>48</v>
       </c>
       <c r="F286" s="2" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -12154,9 +10900,6 @@
         <v>480</v>
       </c>
       <c r="F287" s="2" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -12181,8 +10924,6 @@
         <v>60</v>
       </c>
       <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>8809941826678 / 8809941827477</t>
@@ -12212,9 +10953,6 @@
         <v>50</v>
       </c>
       <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -12239,8 +10977,6 @@
         <v>50</v>
       </c>
       <c r="F290" s="2" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>8809409345963 / 8809941827507</t>
@@ -12270,9 +11006,6 @@
         <v>50</v>
       </c>
       <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -12297,9 +11030,6 @@
         <v>60</v>
       </c>
       <c r="F292" s="2" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -12324,9 +11054,6 @@
         <v>30</v>
       </c>
       <c r="F293" s="2" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -12351,9 +11078,6 @@
         <v>150</v>
       </c>
       <c r="F294" s="2" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -12378,9 +11102,6 @@
         <v>86</v>
       </c>
       <c r="F295" s="2" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -12405,8 +11126,6 @@
         <v>70</v>
       </c>
       <c r="F296" s="2" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>8809409342634 / 8809941827422</t>
@@ -12436,9 +11155,6 @@
         <v>150</v>
       </c>
       <c r="F297" s="2" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -12463,9 +11179,6 @@
         <v>48</v>
       </c>
       <c r="F298" s="2" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -12490,9 +11203,6 @@
         <v>50</v>
       </c>
       <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -12517,8 +11227,6 @@
         <v>60</v>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>8809941825954 / 8809941827057</t>
@@ -12548,9 +11256,6 @@
         <v>300</v>
       </c>
       <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -12575,9 +11280,6 @@
         <v>54</v>
       </c>
       <c r="F302" s="2" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -12602,8 +11304,6 @@
         <v>154</v>
       </c>
       <c r="F303" s="2" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>8809941823158 / 8809941826708</t>
@@ -12633,8 +11333,6 @@
         <v>50</v>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>8809409347462 / 8809941827538</t>
@@ -12664,9 +11362,6 @@
         <v>56</v>
       </c>
       <c r="F305" s="2" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -12691,9 +11386,6 @@
         <v>100</v>
       </c>
       <c r="F306" s="2" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -12718,8 +11410,6 @@
         <v>40</v>
       </c>
       <c r="F307" s="2" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>8809941820690 / 8809941820706</t>
@@ -12749,9 +11439,6 @@
         <v>48</v>
       </c>
       <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -12776,9 +11463,6 @@
         <v>30</v>
       </c>
       <c r="F309" s="2" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -12803,9 +11487,6 @@
         <v>20</v>
       </c>
       <c r="F310" s="2" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -12830,9 +11511,6 @@
         <v>100</v>
       </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -12857,8 +11535,6 @@
         <v>40</v>
       </c>
       <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>8809409345901 / 8809941827408</t>
@@ -12888,9 +11564,6 @@
         <v>60</v>
       </c>
       <c r="F313" s="2" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -12915,9 +11588,6 @@
         <v>20</v>
       </c>
       <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -12942,8 +11612,6 @@
         <v>56</v>
       </c>
       <c r="F315" s="2" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>8809409345895 / 8809941827378</t>
@@ -12973,9 +11641,6 @@
         <v>60</v>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -13000,8 +11665,6 @@
         <v>121</v>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>8809409340432 / 8809941827491</t>
@@ -13031,9 +11694,6 @@
         <v>36</v>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
-      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -13058,9 +11718,6 @@
         <v>120</v>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
-      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -13085,8 +11742,6 @@
         <v>77</v>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>8809409342887 / 8809941827095</t>
@@ -13116,9 +11771,6 @@
         <v>77</v>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -13143,9 +11795,6 @@
         <v>130</v>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -13170,9 +11819,6 @@
         <v>50</v>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -13197,9 +11843,6 @@
         <v>56</v>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -13224,8 +11867,6 @@
         <v>60</v>
       </c>
       <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>8809409346656 / 8809941827187</t>
@@ -13255,9 +11896,6 @@
         <v>150</v>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -13282,9 +11920,6 @@
         <v>100</v>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
-      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -13309,8 +11944,6 @@
         <v>195</v>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>8809409340319 / 8809941826531</t>
@@ -13340,8 +11973,6 @@
         <v>40</v>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>8809941821802 / 8809941827170</t>
@@ -13371,9 +12002,6 @@
         <v>100</v>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -13398,8 +12026,6 @@
         <v>40</v>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>8809941820386 / 8809941827163</t>
@@ -13429,8 +12055,6 @@
         <v>40</v>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>8809941820416 / 8809941827248</t>
@@ -13460,8 +12084,6 @@
         <v>70</v>
       </c>
       <c r="F333" s="2" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>8809941822243 / 8809941827453</t>
@@ -13491,8 +12113,6 @@
         <v>50</v>
       </c>
       <c r="F334" s="2" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>8809941822236 / 8809941827460</t>
@@ -13522,9 +12142,6 @@
         <v>84</v>
       </c>
       <c r="F335" s="2" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -13549,8 +12166,6 @@
         <v>150</v>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>8809409341422 / 8809941826494</t>
@@ -13580,8 +12195,6 @@
         <v>50</v>
       </c>
       <c r="F337" s="2" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>8809409341347 / 8809941826470</t>
@@ -13611,8 +12224,6 @@
         <v>40</v>
       </c>
       <c r="F338" s="2" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>8809409344683 / 8809941826449</t>
@@ -13642,8 +12253,6 @@
         <v>40</v>
       </c>
       <c r="F339" s="2" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>8809409344676 / 8809941826432</t>
@@ -13673,9 +12282,6 @@
         <v>50</v>
       </c>
       <c r="F340" s="2" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -13700,9 +12306,6 @@
         <v>10</v>
       </c>
       <c r="F341" s="2" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr"/>
-      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -13727,8 +12330,6 @@
         <v>117</v>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>8809409343327 / 8809941827484</t>
@@ -13758,8 +12359,6 @@
         <v>40</v>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>8809941820447 / 8809941827224</t>
@@ -13789,9 +12388,6 @@
         <v>150</v>
       </c>
       <c r="F344" s="2" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
-      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -13816,8 +12412,6 @@
         <v>200</v>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>8809409349961 / 8809941827385</t>
@@ -13847,8 +12441,6 @@
         <v>154</v>
       </c>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>8809409341705 / 8809941827354</t>
@@ -13878,9 +12470,6 @@
         <v>200</v>
       </c>
       <c r="F347" s="2" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
-      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -13905,8 +12494,6 @@
         <v>50</v>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>8809409347455 / 8809409347578 / 8809941827361</t>
@@ -13936,8 +12523,6 @@
         <v>54</v>
       </c>
       <c r="F349" s="2" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>8809409348308 / 8809941827392</t>
@@ -13967,8 +12552,6 @@
         <v>40</v>
       </c>
       <c r="F350" s="2" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>8809941822168 / 8809941827132</t>
@@ -13998,8 +12581,6 @@
         <v>50</v>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>8809941822175 / 8809941827149</t>
@@ -14029,9 +12610,6 @@
         <v>300</v>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -14056,8 +12634,6 @@
         <v>60</v>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>8809941825688 / 8809941826944</t>
@@ -14087,8 +12663,6 @@
         <v>30</v>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>8809941824995 / 8809941825053</t>
@@ -14118,9 +12692,6 @@
         <v>56</v>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -14145,9 +12716,6 @@
         <v>100</v>
       </c>
       <c r="F356" s="2" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
-      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -14172,9 +12740,6 @@
         <v>100</v>
       </c>
       <c r="F357" s="2" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -14199,9 +12764,6 @@
         <v>20</v>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
-      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -14226,8 +12788,6 @@
         <v>72</v>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>8809409343655 / 8809941827071</t>
@@ -14257,9 +12817,6 @@
         <v>72</v>
       </c>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -14284,8 +12841,6 @@
         <v>72</v>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
           <t>8809409343648 / 8809941827088</t>
@@ -14315,8 +12870,6 @@
         <v>72</v>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>8809409343662 / 8809941826463</t>
@@ -14346,8 +12899,6 @@
         <v>50</v>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr">
         <is>
           <t>8809409346458 / 8809941827262</t>
@@ -14377,8 +12928,6 @@
         <v>60</v>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>8809409346489 / 8809941827217</t>
@@ -14408,8 +12957,6 @@
         <v>50</v>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
           <t>8809409342474 / 8809941827200</t>
@@ -14439,9 +12986,6 @@
         <v>2880</v>
       </c>
       <c r="F366" s="2" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -14466,9 +13010,6 @@
         <v>3000</v>
       </c>
       <c r="F367" s="2" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
-      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -14493,9 +13034,6 @@
         <v>2880</v>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
-      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -14520,9 +13058,6 @@
         <v>2400</v>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
-      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -14547,9 +13082,6 @@
         <v>200</v>
       </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -14574,9 +13106,6 @@
         <v>100</v>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
-      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -14601,9 +13130,6 @@
         <v>100</v>
       </c>
       <c r="F372" s="2" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -14628,9 +13154,6 @@
         <v>100</v>
       </c>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
-      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -14655,9 +13178,6 @@
         <v>100</v>
       </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -14682,9 +13202,6 @@
         <v>100</v>
       </c>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
-      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -14709,9 +13226,6 @@
         <v>100</v>
       </c>
       <c r="F376" s="2" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -14736,9 +13250,6 @@
         <v>100</v>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
-      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -14763,9 +13274,6 @@
         <v>100</v>
       </c>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -14790,9 +13298,6 @@
         <v>200</v>
       </c>
       <c r="F379" s="2" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
-      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -14803,7 +13308,6 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [BERRY] 3g</t>
@@ -14813,9 +13317,6 @@
         <v>3000</v>
       </c>
       <c r="F380" s="2" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
-      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -14826,7 +13327,6 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [GUMMY BEAR] 3g</t>
@@ -14836,9 +13336,6 @@
         <v>2000</v>
       </c>
       <c r="F381" s="2" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr"/>
-      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -14849,7 +13346,6 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [SWEET CANDY] 3g</t>
@@ -14859,9 +13355,6 @@
         <v>2000</v>
       </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr"/>
-      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -14872,7 +13365,6 @@
           <t>Laneige</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>LIP SLEEPING MASK EX [MANGO] 3g</t>
@@ -14882,9 +13374,6 @@
         <v>2000</v>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr"/>
-      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr"/>
